--- a/template_form.xlsx
+++ b/template_form.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\THANAWAT\TRAINING PYTHON\ECR_System(EMAIL ALERT)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\THANAWAT\TRAININGPYTHON\ECR_System(EMAILALERT)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58119085-751E-48B4-B29E-D1AB61BCE772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FFF925C-0E8B-41BA-AF91-1B025A707E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7BEAB80B-3CB0-4569-BAF5-EBDFCCF99681}"/>
   </bookViews>
@@ -932,97 +932,91 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1055,15 +1049,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1071,15 +1056,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1100,69 +1076,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1174,6 +1087,93 @@
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3029,64 +3029,64 @@
       <c r="A3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
       <c r="N3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
-      <c r="R3" s="101"/>
-      <c r="S3" s="101"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="99"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="99"/>
       <c r="U3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="X3" s="103"/>
-      <c r="Y3" s="103"/>
-      <c r="Z3" s="103"/>
-      <c r="AA3" s="103"/>
+      <c r="X3" s="101"/>
+      <c r="Y3" s="101"/>
+      <c r="Z3" s="101"/>
+      <c r="AA3" s="101"/>
     </row>
     <row r="4" spans="1:37" s="22" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
       <c r="U4" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="X4" s="102"/>
-      <c r="Y4" s="102"/>
-      <c r="Z4" s="102"/>
-      <c r="AA4" s="102"/>
+      <c r="X4" s="100"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="100"/>
+      <c r="AA4" s="100"/>
     </row>
     <row r="5" spans="1:37" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
       <c r="M5" s="2"/>
       <c r="P5" s="2" t="s">
         <v>64</v>
@@ -3104,15 +3104,15 @@
     </row>
     <row r="6" spans="1:37" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="7" spans="1:37" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="117" t="s">
+      <c r="A7" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="104" t="s">
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="102" t="s">
         <v>25</v>
       </c>
       <c r="H7" s="60"/>
@@ -3121,12 +3121,12 @@
       <c r="K7" s="60"/>
       <c r="L7" s="60"/>
       <c r="M7" s="61"/>
-      <c r="O7" s="106" t="s">
+      <c r="O7" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="P7" s="107"/>
-      <c r="Q7" s="107"/>
-      <c r="R7" s="108"/>
+      <c r="P7" s="87"/>
+      <c r="Q7" s="87"/>
+      <c r="R7" s="88"/>
       <c r="S7" s="54" t="s">
         <v>41</v>
       </c>
@@ -3135,32 +3135,32 @@
       <c r="V7" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="W7" s="98"/>
-      <c r="X7" s="98"/>
-      <c r="Y7" s="98"/>
-      <c r="Z7" s="98"/>
+      <c r="W7" s="96"/>
+      <c r="X7" s="96"/>
+      <c r="Y7" s="96"/>
+      <c r="Z7" s="96"/>
       <c r="AA7" s="20"/>
     </row>
     <row r="8" spans="1:37" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="119" t="s">
+      <c r="A8" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="97"/>
-      <c r="O8" s="109"/>
-      <c r="P8" s="110"/>
-      <c r="Q8" s="110"/>
-      <c r="R8" s="111"/>
+      <c r="B8" s="112"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
+      <c r="J8" s="94"/>
+      <c r="K8" s="94"/>
+      <c r="L8" s="94"/>
+      <c r="M8" s="95"/>
+      <c r="O8" s="104"/>
+      <c r="P8" s="105"/>
+      <c r="Q8" s="105"/>
+      <c r="R8" s="106"/>
       <c r="S8" s="38" t="s">
         <v>27</v>
       </c>
@@ -3168,32 +3168,32 @@
       <c r="V8" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="W8" s="99"/>
-      <c r="X8" s="99"/>
-      <c r="Y8" s="99"/>
-      <c r="Z8" s="99"/>
+      <c r="W8" s="97"/>
+      <c r="X8" s="97"/>
+      <c r="Y8" s="97"/>
+      <c r="Z8" s="97"/>
       <c r="AA8" s="23"/>
     </row>
     <row r="9" spans="1:37" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="115" t="s">
+      <c r="A9" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="116"/>
-      <c r="C9" s="116"/>
-      <c r="D9" s="116"/>
-      <c r="E9" s="116"/>
-      <c r="F9" s="116"/>
-      <c r="G9" s="105"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="103"/>
       <c r="H9" s="52"/>
       <c r="I9" s="52"/>
       <c r="J9" s="52"/>
       <c r="K9" s="52"/>
       <c r="L9" s="52"/>
       <c r="M9" s="62"/>
-      <c r="O9" s="109"/>
-      <c r="P9" s="110"/>
-      <c r="Q9" s="110"/>
-      <c r="R9" s="111"/>
+      <c r="O9" s="104"/>
+      <c r="P9" s="105"/>
+      <c r="Q9" s="105"/>
+      <c r="R9" s="106"/>
       <c r="S9" s="38" t="s">
         <v>28</v>
       </c>
@@ -3201,10 +3201,10 @@
       <c r="V9" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="W9" s="99"/>
-      <c r="X9" s="99"/>
-      <c r="Y9" s="99"/>
-      <c r="Z9" s="99"/>
+      <c r="W9" s="97"/>
+      <c r="X9" s="97"/>
+      <c r="Y9" s="97"/>
+      <c r="Z9" s="97"/>
       <c r="AA9" s="23"/>
     </row>
     <row r="10" spans="1:37" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
@@ -3221,10 +3221,10 @@
       <c r="K10" s="36"/>
       <c r="L10" s="36"/>
       <c r="M10" s="37"/>
-      <c r="O10" s="112"/>
-      <c r="P10" s="113"/>
-      <c r="Q10" s="113"/>
-      <c r="R10" s="114"/>
+      <c r="O10" s="86"/>
+      <c r="P10" s="89"/>
+      <c r="Q10" s="89"/>
+      <c r="R10" s="90"/>
       <c r="S10" s="24"/>
       <c r="T10" s="24"/>
       <c r="U10" s="18"/>
@@ -3244,85 +3244,85 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="142"/>
-      <c r="E12" s="142"/>
-      <c r="F12" s="142"/>
-      <c r="G12" s="142"/>
-      <c r="H12" s="142"/>
-      <c r="I12" s="142"/>
-      <c r="J12" s="142"/>
-      <c r="K12" s="142"/>
-      <c r="L12" s="142"/>
-      <c r="M12" s="142"/>
-      <c r="N12" s="142"/>
-      <c r="O12" s="142"/>
-      <c r="P12" s="142"/>
-      <c r="Q12" s="142"/>
-      <c r="R12" s="142"/>
-      <c r="S12" s="142"/>
-      <c r="T12" s="142"/>
-      <c r="U12" s="142"/>
-      <c r="V12" s="142"/>
-      <c r="W12" s="142"/>
-      <c r="X12" s="142"/>
-      <c r="Y12" s="142"/>
-      <c r="Z12" s="142"/>
-      <c r="AA12" s="143"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="113"/>
+      <c r="J12" s="113"/>
+      <c r="K12" s="113"/>
+      <c r="L12" s="113"/>
+      <c r="M12" s="113"/>
+      <c r="N12" s="113"/>
+      <c r="O12" s="113"/>
+      <c r="P12" s="113"/>
+      <c r="Q12" s="113"/>
+      <c r="R12" s="113"/>
+      <c r="S12" s="113"/>
+      <c r="T12" s="113"/>
+      <c r="U12" s="113"/>
+      <c r="V12" s="113"/>
+      <c r="W12" s="113"/>
+      <c r="X12" s="113"/>
+      <c r="Y12" s="113"/>
+      <c r="Z12" s="113"/>
+      <c r="AA12" s="114"/>
     </row>
     <row r="13" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="31"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="144"/>
-      <c r="L13" s="144"/>
-      <c r="M13" s="144"/>
-      <c r="N13" s="144"/>
-      <c r="O13" s="144"/>
-      <c r="P13" s="144"/>
-      <c r="Q13" s="144"/>
-      <c r="R13" s="144"/>
-      <c r="S13" s="144"/>
-      <c r="T13" s="144"/>
-      <c r="U13" s="144"/>
-      <c r="V13" s="144"/>
-      <c r="W13" s="144"/>
-      <c r="X13" s="144"/>
-      <c r="Y13" s="144"/>
-      <c r="Z13" s="144"/>
-      <c r="AA13" s="145"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="115"/>
+      <c r="K13" s="115"/>
+      <c r="L13" s="115"/>
+      <c r="M13" s="115"/>
+      <c r="N13" s="115"/>
+      <c r="O13" s="115"/>
+      <c r="P13" s="115"/>
+      <c r="Q13" s="115"/>
+      <c r="R13" s="115"/>
+      <c r="S13" s="115"/>
+      <c r="T13" s="115"/>
+      <c r="U13" s="115"/>
+      <c r="V13" s="115"/>
+      <c r="W13" s="115"/>
+      <c r="X13" s="115"/>
+      <c r="Y13" s="115"/>
+      <c r="Z13" s="115"/>
+      <c r="AA13" s="116"/>
     </row>
     <row r="14" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A14" s="31"/>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="144"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="144"/>
-      <c r="L14" s="144"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="144"/>
-      <c r="P14" s="144"/>
-      <c r="Q14" s="144"/>
-      <c r="R14" s="144"/>
-      <c r="S14" s="144"/>
-      <c r="T14" s="144"/>
-      <c r="U14" s="144"/>
-      <c r="V14" s="144"/>
-      <c r="W14" s="144"/>
-      <c r="X14" s="144"/>
-      <c r="Y14" s="144"/>
-      <c r="Z14" s="144"/>
-      <c r="AA14" s="145"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="115"/>
+      <c r="K14" s="115"/>
+      <c r="L14" s="115"/>
+      <c r="M14" s="115"/>
+      <c r="N14" s="115"/>
+      <c r="O14" s="115"/>
+      <c r="P14" s="115"/>
+      <c r="Q14" s="115"/>
+      <c r="R14" s="115"/>
+      <c r="S14" s="115"/>
+      <c r="T14" s="115"/>
+      <c r="U14" s="115"/>
+      <c r="V14" s="115"/>
+      <c r="W14" s="115"/>
+      <c r="X14" s="115"/>
+      <c r="Y14" s="115"/>
+      <c r="Z14" s="115"/>
+      <c r="AA14" s="116"/>
     </row>
     <row r="15" spans="1:37" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A15" s="5"/>
@@ -3355,86 +3355,86 @@
     </row>
     <row r="16" spans="1:37" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="17" spans="1:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A17" s="106" t="s">
+      <c r="A17" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="106" t="s">
+      <c r="B17" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="107"/>
-      <c r="D17" s="107"/>
-      <c r="E17" s="107"/>
-      <c r="F17" s="107"/>
-      <c r="G17" s="107"/>
-      <c r="H17" s="107"/>
-      <c r="I17" s="107"/>
-      <c r="J17" s="108"/>
-      <c r="K17" s="121" t="s">
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="87"/>
+      <c r="I17" s="87"/>
+      <c r="J17" s="88"/>
+      <c r="K17" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="L17" s="126"/>
-      <c r="M17" s="126"/>
-      <c r="N17" s="122"/>
-      <c r="O17" s="106" t="s">
+      <c r="L17" s="92"/>
+      <c r="M17" s="92"/>
+      <c r="N17" s="93"/>
+      <c r="O17" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="P17" s="107"/>
-      <c r="Q17" s="107"/>
-      <c r="R17" s="108"/>
-      <c r="S17" s="106" t="s">
+      <c r="P17" s="87"/>
+      <c r="Q17" s="87"/>
+      <c r="R17" s="88"/>
+      <c r="S17" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="T17" s="108"/>
-      <c r="U17" s="106" t="s">
+      <c r="T17" s="88"/>
+      <c r="U17" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="V17" s="107"/>
-      <c r="W17" s="107"/>
-      <c r="X17" s="107"/>
-      <c r="Y17" s="106" t="s">
+      <c r="V17" s="87"/>
+      <c r="W17" s="87"/>
+      <c r="X17" s="87"/>
+      <c r="Y17" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="Z17" s="107"/>
-      <c r="AA17" s="108"/>
+      <c r="Z17" s="87"/>
+      <c r="AA17" s="88"/>
     </row>
     <row r="18" spans="1:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A18" s="112"/>
-      <c r="B18" s="112"/>
-      <c r="C18" s="113"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="113"/>
-      <c r="F18" s="113"/>
-      <c r="G18" s="113"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="113"/>
-      <c r="J18" s="114"/>
-      <c r="K18" s="121" t="s">
+      <c r="A18" s="86"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="L18" s="122"/>
-      <c r="M18" s="121" t="s">
+      <c r="L18" s="93"/>
+      <c r="M18" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="122"/>
-      <c r="O18" s="112" t="s">
+      <c r="N18" s="93"/>
+      <c r="O18" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="P18" s="113"/>
-      <c r="Q18" s="113"/>
-      <c r="R18" s="114"/>
-      <c r="S18" s="112"/>
-      <c r="T18" s="114"/>
-      <c r="U18" s="123" t="s">
+      <c r="P18" s="89"/>
+      <c r="Q18" s="89"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="86"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="124"/>
-      <c r="W18" s="124"/>
-      <c r="X18" s="124"/>
-      <c r="Y18" s="123" t="s">
+      <c r="V18" s="129"/>
+      <c r="W18" s="129"/>
+      <c r="X18" s="129"/>
+      <c r="Y18" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="Z18" s="124"/>
-      <c r="AA18" s="125"/>
+      <c r="Z18" s="129"/>
+      <c r="AA18" s="130"/>
     </row>
     <row r="19" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A19" s="8">
@@ -3451,25 +3451,25 @@
       <c r="H19" s="40"/>
       <c r="I19" s="40"/>
       <c r="J19" s="41"/>
-      <c r="K19" s="94"/>
-      <c r="L19" s="95"/>
-      <c r="M19" s="94"/>
-      <c r="N19" s="95"/>
-      <c r="O19" s="88"/>
-      <c r="P19" s="89"/>
-      <c r="Q19" s="89"/>
-      <c r="R19" s="90"/>
-      <c r="S19" s="88" t="s">
+      <c r="K19" s="126"/>
+      <c r="L19" s="127"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="127"/>
+      <c r="O19" s="117"/>
+      <c r="P19" s="118"/>
+      <c r="Q19" s="118"/>
+      <c r="R19" s="119"/>
+      <c r="S19" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="T19" s="90"/>
-      <c r="U19" s="91"/>
-      <c r="V19" s="92"/>
-      <c r="W19" s="92"/>
-      <c r="X19" s="93"/>
-      <c r="Y19" s="91"/>
-      <c r="Z19" s="92"/>
-      <c r="AA19" s="93"/>
+      <c r="T19" s="119"/>
+      <c r="U19" s="120"/>
+      <c r="V19" s="121"/>
+      <c r="W19" s="121"/>
+      <c r="X19" s="122"/>
+      <c r="Y19" s="120"/>
+      <c r="Z19" s="121"/>
+      <c r="AA19" s="122"/>
     </row>
     <row r="20" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="11">
@@ -3486,25 +3486,25 @@
       <c r="H20" s="43"/>
       <c r="I20" s="43"/>
       <c r="J20" s="44"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="65"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="76"/>
-      <c r="P20" s="77"/>
-      <c r="Q20" s="77"/>
-      <c r="R20" s="78"/>
-      <c r="S20" s="76" t="s">
+      <c r="K20" s="83"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="83"/>
+      <c r="N20" s="84"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="81"/>
+      <c r="Q20" s="81"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="T20" s="78"/>
-      <c r="U20" s="79"/>
-      <c r="V20" s="80"/>
-      <c r="W20" s="80"/>
-      <c r="X20" s="81"/>
-      <c r="Y20" s="79"/>
-      <c r="Z20" s="80"/>
-      <c r="AA20" s="81"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="123"/>
+      <c r="V20" s="124"/>
+      <c r="W20" s="124"/>
+      <c r="X20" s="125"/>
+      <c r="Y20" s="123"/>
+      <c r="Z20" s="124"/>
+      <c r="AA20" s="125"/>
     </row>
     <row r="21" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A21" s="11">
@@ -3521,25 +3521,25 @@
       <c r="H21" s="43"/>
       <c r="I21" s="43"/>
       <c r="J21" s="44"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="76"/>
-      <c r="P21" s="77"/>
-      <c r="Q21" s="77"/>
-      <c r="R21" s="78"/>
-      <c r="S21" s="76" t="s">
+      <c r="K21" s="83"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="83"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="81"/>
+      <c r="Q21" s="81"/>
+      <c r="R21" s="82"/>
+      <c r="S21" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="T21" s="78"/>
-      <c r="U21" s="79"/>
-      <c r="V21" s="80"/>
-      <c r="W21" s="80"/>
-      <c r="X21" s="81"/>
-      <c r="Y21" s="79"/>
-      <c r="Z21" s="80"/>
-      <c r="AA21" s="81"/>
+      <c r="T21" s="82"/>
+      <c r="U21" s="123"/>
+      <c r="V21" s="124"/>
+      <c r="W21" s="124"/>
+      <c r="X21" s="125"/>
+      <c r="Y21" s="123"/>
+      <c r="Z21" s="124"/>
+      <c r="AA21" s="125"/>
     </row>
     <row r="22" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="11">
@@ -3556,25 +3556,25 @@
       <c r="H22" s="43"/>
       <c r="I22" s="43"/>
       <c r="J22" s="44"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="76"/>
-      <c r="P22" s="77"/>
-      <c r="Q22" s="77"/>
-      <c r="R22" s="78"/>
-      <c r="S22" s="76" t="s">
+      <c r="K22" s="83"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="83"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="80"/>
+      <c r="P22" s="81"/>
+      <c r="Q22" s="81"/>
+      <c r="R22" s="82"/>
+      <c r="S22" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="T22" s="78"/>
-      <c r="U22" s="79"/>
-      <c r="V22" s="80"/>
-      <c r="W22" s="80"/>
-      <c r="X22" s="81"/>
-      <c r="Y22" s="79"/>
-      <c r="Z22" s="80"/>
-      <c r="AA22" s="81"/>
+      <c r="T22" s="82"/>
+      <c r="U22" s="123"/>
+      <c r="V22" s="124"/>
+      <c r="W22" s="124"/>
+      <c r="X22" s="125"/>
+      <c r="Y22" s="123"/>
+      <c r="Z22" s="124"/>
+      <c r="AA22" s="125"/>
     </row>
     <row r="23" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A23" s="11">
@@ -3591,34 +3591,34 @@
       <c r="H23" s="43"/>
       <c r="I23" s="43"/>
       <c r="J23" s="44"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="76"/>
-      <c r="P23" s="77"/>
-      <c r="Q23" s="77"/>
-      <c r="R23" s="78"/>
-      <c r="S23" s="76" t="s">
+      <c r="K23" s="83"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="80"/>
+      <c r="P23" s="81"/>
+      <c r="Q23" s="81"/>
+      <c r="R23" s="82"/>
+      <c r="S23" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="T23" s="78"/>
-      <c r="U23" s="79"/>
-      <c r="V23" s="80"/>
-      <c r="W23" s="80"/>
-      <c r="X23" s="81"/>
-      <c r="Y23" s="79"/>
-      <c r="Z23" s="80"/>
-      <c r="AA23" s="81"/>
+      <c r="T23" s="82"/>
+      <c r="U23" s="123"/>
+      <c r="V23" s="124"/>
+      <c r="W23" s="124"/>
+      <c r="X23" s="125"/>
+      <c r="Y23" s="123"/>
+      <c r="Z23" s="124"/>
+      <c r="AA23" s="125"/>
     </row>
     <row r="24" spans="1:27" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="63">
         <v>6</v>
       </c>
-      <c r="B24" s="127" t="s">
+      <c r="B24" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="128"/>
+      <c r="C24" s="77"/>
       <c r="D24" s="45"/>
       <c r="E24" s="45"/>
       <c r="F24" s="45"/>
@@ -3626,25 +3626,25 @@
       <c r="H24" s="45"/>
       <c r="I24" s="45"/>
       <c r="J24" s="46"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="70"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="70"/>
-      <c r="O24" s="82"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="84"/>
-      <c r="S24" s="140" t="s">
+      <c r="K24" s="142"/>
+      <c r="L24" s="143"/>
+      <c r="M24" s="142"/>
+      <c r="N24" s="143"/>
+      <c r="O24" s="131"/>
+      <c r="P24" s="132"/>
+      <c r="Q24" s="132"/>
+      <c r="R24" s="133"/>
+      <c r="S24" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="T24" s="141"/>
-      <c r="U24" s="85"/>
-      <c r="V24" s="86"/>
-      <c r="W24" s="86"/>
-      <c r="X24" s="87"/>
-      <c r="Y24" s="85"/>
-      <c r="Z24" s="86"/>
-      <c r="AA24" s="87"/>
+      <c r="T24" s="79"/>
+      <c r="U24" s="134"/>
+      <c r="V24" s="135"/>
+      <c r="W24" s="135"/>
+      <c r="X24" s="136"/>
+      <c r="Y24" s="134"/>
+      <c r="Z24" s="135"/>
+      <c r="AA24" s="136"/>
     </row>
     <row r="25" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="11">
@@ -3661,25 +3661,25 @@
       <c r="H25" s="43"/>
       <c r="I25" s="43"/>
       <c r="J25" s="44"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="65"/>
-      <c r="N25" s="66"/>
-      <c r="O25" s="76"/>
-      <c r="P25" s="77"/>
-      <c r="Q25" s="77"/>
-      <c r="R25" s="78"/>
-      <c r="S25" s="76" t="s">
+      <c r="K25" s="83"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="83"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="80"/>
+      <c r="P25" s="81"/>
+      <c r="Q25" s="81"/>
+      <c r="R25" s="82"/>
+      <c r="S25" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="T25" s="78"/>
-      <c r="U25" s="79"/>
-      <c r="V25" s="80"/>
-      <c r="W25" s="80"/>
-      <c r="X25" s="81"/>
-      <c r="Y25" s="79"/>
-      <c r="Z25" s="80"/>
-      <c r="AA25" s="81"/>
+      <c r="T25" s="82"/>
+      <c r="U25" s="123"/>
+      <c r="V25" s="124"/>
+      <c r="W25" s="124"/>
+      <c r="X25" s="125"/>
+      <c r="Y25" s="123"/>
+      <c r="Z25" s="124"/>
+      <c r="AA25" s="125"/>
     </row>
     <row r="26" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A26" s="11">
@@ -3696,25 +3696,25 @@
       <c r="H26" s="43"/>
       <c r="I26" s="43"/>
       <c r="J26" s="44"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="66"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="76"/>
-      <c r="P26" s="77"/>
-      <c r="Q26" s="77"/>
-      <c r="R26" s="78"/>
-      <c r="S26" s="76" t="s">
+      <c r="K26" s="83"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="83"/>
+      <c r="N26" s="84"/>
+      <c r="O26" s="80"/>
+      <c r="P26" s="81"/>
+      <c r="Q26" s="81"/>
+      <c r="R26" s="82"/>
+      <c r="S26" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="T26" s="78"/>
-      <c r="U26" s="79"/>
-      <c r="V26" s="80"/>
-      <c r="W26" s="80"/>
-      <c r="X26" s="81"/>
-      <c r="Y26" s="79"/>
-      <c r="Z26" s="80"/>
-      <c r="AA26" s="81"/>
+      <c r="T26" s="82"/>
+      <c r="U26" s="123"/>
+      <c r="V26" s="124"/>
+      <c r="W26" s="124"/>
+      <c r="X26" s="125"/>
+      <c r="Y26" s="123"/>
+      <c r="Z26" s="124"/>
+      <c r="AA26" s="125"/>
     </row>
     <row r="27" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A27" s="11">
@@ -3731,25 +3731,25 @@
       <c r="H27" s="43"/>
       <c r="I27" s="43"/>
       <c r="J27" s="44"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="65"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="76"/>
-      <c r="P27" s="77"/>
-      <c r="Q27" s="77"/>
-      <c r="R27" s="78"/>
-      <c r="S27" s="76" t="s">
+      <c r="K27" s="83"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="83"/>
+      <c r="N27" s="84"/>
+      <c r="O27" s="80"/>
+      <c r="P27" s="81"/>
+      <c r="Q27" s="81"/>
+      <c r="R27" s="82"/>
+      <c r="S27" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="T27" s="78"/>
-      <c r="U27" s="79"/>
-      <c r="V27" s="80"/>
-      <c r="W27" s="80"/>
-      <c r="X27" s="81"/>
-      <c r="Y27" s="79"/>
-      <c r="Z27" s="80"/>
-      <c r="AA27" s="81"/>
+      <c r="T27" s="82"/>
+      <c r="U27" s="123"/>
+      <c r="V27" s="124"/>
+      <c r="W27" s="124"/>
+      <c r="X27" s="125"/>
+      <c r="Y27" s="123"/>
+      <c r="Z27" s="124"/>
+      <c r="AA27" s="125"/>
     </row>
     <row r="28" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A28" s="11">
@@ -3766,25 +3766,25 @@
       <c r="H28" s="43"/>
       <c r="I28" s="43"/>
       <c r="J28" s="44"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="76"/>
-      <c r="P28" s="77"/>
-      <c r="Q28" s="77"/>
-      <c r="R28" s="78"/>
-      <c r="S28" s="76" t="s">
+      <c r="K28" s="83"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="83"/>
+      <c r="N28" s="84"/>
+      <c r="O28" s="80"/>
+      <c r="P28" s="81"/>
+      <c r="Q28" s="81"/>
+      <c r="R28" s="82"/>
+      <c r="S28" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="T28" s="78"/>
-      <c r="U28" s="79"/>
-      <c r="V28" s="80"/>
-      <c r="W28" s="80"/>
-      <c r="X28" s="81"/>
-      <c r="Y28" s="79"/>
-      <c r="Z28" s="80"/>
-      <c r="AA28" s="81"/>
+      <c r="T28" s="82"/>
+      <c r="U28" s="123"/>
+      <c r="V28" s="124"/>
+      <c r="W28" s="124"/>
+      <c r="X28" s="125"/>
+      <c r="Y28" s="123"/>
+      <c r="Z28" s="124"/>
+      <c r="AA28" s="125"/>
     </row>
     <row r="29" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A29" s="11">
@@ -3801,25 +3801,25 @@
       <c r="H29" s="43"/>
       <c r="I29" s="43"/>
       <c r="J29" s="44"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="66"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="66"/>
-      <c r="O29" s="76"/>
-      <c r="P29" s="77"/>
-      <c r="Q29" s="77"/>
-      <c r="R29" s="78"/>
-      <c r="S29" s="76" t="s">
+      <c r="K29" s="83"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="83"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="80"/>
+      <c r="P29" s="81"/>
+      <c r="Q29" s="81"/>
+      <c r="R29" s="82"/>
+      <c r="S29" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="T29" s="78"/>
-      <c r="U29" s="79"/>
-      <c r="V29" s="80"/>
-      <c r="W29" s="80"/>
-      <c r="X29" s="81"/>
-      <c r="Y29" s="79"/>
-      <c r="Z29" s="80"/>
-      <c r="AA29" s="81"/>
+      <c r="T29" s="82"/>
+      <c r="U29" s="123"/>
+      <c r="V29" s="124"/>
+      <c r="W29" s="124"/>
+      <c r="X29" s="125"/>
+      <c r="Y29" s="123"/>
+      <c r="Z29" s="124"/>
+      <c r="AA29" s="125"/>
     </row>
     <row r="30" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A30" s="11">
@@ -3836,25 +3836,25 @@
       <c r="H30" s="43"/>
       <c r="I30" s="43"/>
       <c r="J30" s="44"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="66"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="66"/>
-      <c r="O30" s="76"/>
-      <c r="P30" s="77"/>
-      <c r="Q30" s="77"/>
-      <c r="R30" s="78"/>
-      <c r="S30" s="76" t="s">
+      <c r="K30" s="83"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="83"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="80"/>
+      <c r="P30" s="81"/>
+      <c r="Q30" s="81"/>
+      <c r="R30" s="82"/>
+      <c r="S30" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="T30" s="78"/>
-      <c r="U30" s="79"/>
-      <c r="V30" s="80"/>
-      <c r="W30" s="80"/>
-      <c r="X30" s="81"/>
-      <c r="Y30" s="79"/>
-      <c r="Z30" s="80"/>
-      <c r="AA30" s="81"/>
+      <c r="T30" s="82"/>
+      <c r="U30" s="123"/>
+      <c r="V30" s="124"/>
+      <c r="W30" s="124"/>
+      <c r="X30" s="125"/>
+      <c r="Y30" s="123"/>
+      <c r="Z30" s="124"/>
+      <c r="AA30" s="125"/>
     </row>
     <row r="31" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A31" s="11">
@@ -3871,25 +3871,25 @@
       <c r="H31" s="43"/>
       <c r="I31" s="43"/>
       <c r="J31" s="44"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="66"/>
-      <c r="M31" s="65"/>
-      <c r="N31" s="66"/>
-      <c r="O31" s="76"/>
-      <c r="P31" s="77"/>
-      <c r="Q31" s="77"/>
-      <c r="R31" s="78"/>
-      <c r="S31" s="76" t="s">
+      <c r="K31" s="83"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="83"/>
+      <c r="N31" s="84"/>
+      <c r="O31" s="80"/>
+      <c r="P31" s="81"/>
+      <c r="Q31" s="81"/>
+      <c r="R31" s="82"/>
+      <c r="S31" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="T31" s="78"/>
-      <c r="U31" s="79"/>
-      <c r="V31" s="80"/>
-      <c r="W31" s="80"/>
-      <c r="X31" s="81"/>
-      <c r="Y31" s="79"/>
-      <c r="Z31" s="80"/>
-      <c r="AA31" s="81"/>
+      <c r="T31" s="82"/>
+      <c r="U31" s="123"/>
+      <c r="V31" s="124"/>
+      <c r="W31" s="124"/>
+      <c r="X31" s="125"/>
+      <c r="Y31" s="123"/>
+      <c r="Z31" s="124"/>
+      <c r="AA31" s="125"/>
     </row>
     <row r="32" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A32" s="11">
@@ -3906,25 +3906,25 @@
       <c r="H32" s="43"/>
       <c r="I32" s="43"/>
       <c r="J32" s="44"/>
-      <c r="K32" s="65"/>
-      <c r="L32" s="66"/>
-      <c r="M32" s="65"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="76"/>
-      <c r="P32" s="77"/>
-      <c r="Q32" s="77"/>
-      <c r="R32" s="78"/>
-      <c r="S32" s="76" t="s">
+      <c r="K32" s="83"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="83"/>
+      <c r="N32" s="84"/>
+      <c r="O32" s="80"/>
+      <c r="P32" s="81"/>
+      <c r="Q32" s="81"/>
+      <c r="R32" s="82"/>
+      <c r="S32" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="T32" s="78"/>
-      <c r="U32" s="79"/>
-      <c r="V32" s="80"/>
-      <c r="W32" s="80"/>
-      <c r="X32" s="81"/>
-      <c r="Y32" s="79"/>
-      <c r="Z32" s="80"/>
-      <c r="AA32" s="81"/>
+      <c r="T32" s="82"/>
+      <c r="U32" s="123"/>
+      <c r="V32" s="124"/>
+      <c r="W32" s="124"/>
+      <c r="X32" s="125"/>
+      <c r="Y32" s="123"/>
+      <c r="Z32" s="124"/>
+      <c r="AA32" s="125"/>
     </row>
     <row r="33" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A33" s="11">
@@ -3941,25 +3941,25 @@
       <c r="H33" s="43"/>
       <c r="I33" s="43"/>
       <c r="J33" s="44"/>
-      <c r="K33" s="65"/>
-      <c r="L33" s="66"/>
-      <c r="M33" s="65"/>
-      <c r="N33" s="66"/>
-      <c r="O33" s="76"/>
-      <c r="P33" s="77"/>
-      <c r="Q33" s="77"/>
-      <c r="R33" s="78"/>
-      <c r="S33" s="76" t="s">
+      <c r="K33" s="83"/>
+      <c r="L33" s="84"/>
+      <c r="M33" s="83"/>
+      <c r="N33" s="84"/>
+      <c r="O33" s="80"/>
+      <c r="P33" s="81"/>
+      <c r="Q33" s="81"/>
+      <c r="R33" s="82"/>
+      <c r="S33" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="T33" s="78"/>
-      <c r="U33" s="79"/>
-      <c r="V33" s="80"/>
-      <c r="W33" s="80"/>
-      <c r="X33" s="81"/>
-      <c r="Y33" s="79"/>
-      <c r="Z33" s="80"/>
-      <c r="AA33" s="81"/>
+      <c r="T33" s="82"/>
+      <c r="U33" s="123"/>
+      <c r="V33" s="124"/>
+      <c r="W33" s="124"/>
+      <c r="X33" s="125"/>
+      <c r="Y33" s="123"/>
+      <c r="Z33" s="124"/>
+      <c r="AA33" s="125"/>
     </row>
     <row r="34" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A34" s="11">
@@ -3976,25 +3976,25 @@
       <c r="H34" s="43"/>
       <c r="I34" s="43"/>
       <c r="J34" s="44"/>
-      <c r="K34" s="65"/>
-      <c r="L34" s="66"/>
-      <c r="M34" s="65"/>
-      <c r="N34" s="66"/>
-      <c r="O34" s="76"/>
-      <c r="P34" s="77"/>
-      <c r="Q34" s="77"/>
-      <c r="R34" s="78"/>
-      <c r="S34" s="76" t="s">
+      <c r="K34" s="83"/>
+      <c r="L34" s="84"/>
+      <c r="M34" s="83"/>
+      <c r="N34" s="84"/>
+      <c r="O34" s="80"/>
+      <c r="P34" s="81"/>
+      <c r="Q34" s="81"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="T34" s="78"/>
-      <c r="U34" s="79"/>
-      <c r="V34" s="80"/>
-      <c r="W34" s="80"/>
-      <c r="X34" s="81"/>
-      <c r="Y34" s="79"/>
-      <c r="Z34" s="80"/>
-      <c r="AA34" s="81"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="123"/>
+      <c r="V34" s="124"/>
+      <c r="W34" s="124"/>
+      <c r="X34" s="125"/>
+      <c r="Y34" s="123"/>
+      <c r="Z34" s="124"/>
+      <c r="AA34" s="125"/>
     </row>
     <row r="35" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A35" s="11">
@@ -4011,25 +4011,25 @@
       <c r="H35" s="43"/>
       <c r="I35" s="43"/>
       <c r="J35" s="44"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="66"/>
-      <c r="M35" s="65"/>
-      <c r="N35" s="66"/>
-      <c r="O35" s="76"/>
-      <c r="P35" s="77"/>
-      <c r="Q35" s="77"/>
-      <c r="R35" s="78"/>
-      <c r="S35" s="76" t="s">
+      <c r="K35" s="83"/>
+      <c r="L35" s="84"/>
+      <c r="M35" s="83"/>
+      <c r="N35" s="84"/>
+      <c r="O35" s="80"/>
+      <c r="P35" s="81"/>
+      <c r="Q35" s="81"/>
+      <c r="R35" s="82"/>
+      <c r="S35" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="T35" s="78"/>
-      <c r="U35" s="79"/>
-      <c r="V35" s="80"/>
-      <c r="W35" s="80"/>
-      <c r="X35" s="81"/>
-      <c r="Y35" s="79"/>
-      <c r="Z35" s="80"/>
-      <c r="AA35" s="81"/>
+      <c r="T35" s="82"/>
+      <c r="U35" s="123"/>
+      <c r="V35" s="124"/>
+      <c r="W35" s="124"/>
+      <c r="X35" s="125"/>
+      <c r="Y35" s="123"/>
+      <c r="Z35" s="124"/>
+      <c r="AA35" s="125"/>
     </row>
     <row r="36" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A36" s="11">
@@ -4046,25 +4046,25 @@
       <c r="H36" s="43"/>
       <c r="I36" s="43"/>
       <c r="J36" s="44"/>
-      <c r="K36" s="65"/>
-      <c r="L36" s="66"/>
-      <c r="M36" s="65"/>
-      <c r="N36" s="66"/>
-      <c r="O36" s="76"/>
-      <c r="P36" s="77"/>
-      <c r="Q36" s="77"/>
-      <c r="R36" s="78"/>
-      <c r="S36" s="76" t="s">
+      <c r="K36" s="83"/>
+      <c r="L36" s="84"/>
+      <c r="M36" s="83"/>
+      <c r="N36" s="84"/>
+      <c r="O36" s="80"/>
+      <c r="P36" s="81"/>
+      <c r="Q36" s="81"/>
+      <c r="R36" s="82"/>
+      <c r="S36" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="T36" s="78"/>
-      <c r="U36" s="79"/>
-      <c r="V36" s="80"/>
-      <c r="W36" s="80"/>
-      <c r="X36" s="81"/>
-      <c r="Y36" s="79"/>
-      <c r="Z36" s="80"/>
-      <c r="AA36" s="81"/>
+      <c r="T36" s="82"/>
+      <c r="U36" s="123"/>
+      <c r="V36" s="124"/>
+      <c r="W36" s="124"/>
+      <c r="X36" s="125"/>
+      <c r="Y36" s="123"/>
+      <c r="Z36" s="124"/>
+      <c r="AA36" s="125"/>
     </row>
     <row r="37" spans="1:27" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A37" s="29">
@@ -4081,35 +4081,35 @@
       <c r="H37" s="48"/>
       <c r="I37" s="48"/>
       <c r="J37" s="49"/>
-      <c r="K37" s="67"/>
-      <c r="L37" s="68"/>
-      <c r="M37" s="67"/>
-      <c r="N37" s="68"/>
-      <c r="O37" s="132"/>
-      <c r="P37" s="136"/>
-      <c r="Q37" s="136"/>
-      <c r="R37" s="133"/>
-      <c r="S37" s="132" t="s">
+      <c r="K37" s="140"/>
+      <c r="L37" s="141"/>
+      <c r="M37" s="140"/>
+      <c r="N37" s="141"/>
+      <c r="O37" s="68"/>
+      <c r="P37" s="72"/>
+      <c r="Q37" s="72"/>
+      <c r="R37" s="69"/>
+      <c r="S37" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="T37" s="133"/>
-      <c r="U37" s="137"/>
-      <c r="V37" s="138"/>
-      <c r="W37" s="138"/>
-      <c r="X37" s="139"/>
-      <c r="Y37" s="137"/>
-      <c r="Z37" s="138"/>
-      <c r="AA37" s="139"/>
+      <c r="T37" s="69"/>
+      <c r="U37" s="73"/>
+      <c r="V37" s="74"/>
+      <c r="W37" s="74"/>
+      <c r="X37" s="75"/>
+      <c r="Y37" s="73"/>
+      <c r="Z37" s="74"/>
+      <c r="AA37" s="75"/>
     </row>
     <row r="38" spans="1:27" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="39" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="134" t="s">
+      <c r="A39" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="135"/>
-      <c r="C39" s="135"/>
-      <c r="D39" s="135"/>
-      <c r="E39" s="135"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
       <c r="F39" s="56"/>
       <c r="G39" s="57" t="s">
         <v>23</v>
@@ -4119,31 +4119,31 @@
       <c r="J39" s="54"/>
       <c r="K39" s="56"/>
       <c r="L39" s="55"/>
-      <c r="M39" s="129" t="s">
+      <c r="M39" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="N39" s="130"/>
-      <c r="O39" s="131"/>
-      <c r="P39" s="129" t="s">
+      <c r="N39" s="66"/>
+      <c r="O39" s="67"/>
+      <c r="P39" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="Q39" s="130"/>
-      <c r="R39" s="131"/>
-      <c r="S39" s="129" t="s">
+      <c r="Q39" s="66"/>
+      <c r="R39" s="67"/>
+      <c r="S39" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="T39" s="130"/>
-      <c r="U39" s="131"/>
-      <c r="V39" s="130" t="s">
+      <c r="T39" s="66"/>
+      <c r="U39" s="67"/>
+      <c r="V39" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="W39" s="130"/>
-      <c r="X39" s="131"/>
-      <c r="Y39" s="129" t="s">
+      <c r="W39" s="66"/>
+      <c r="X39" s="67"/>
+      <c r="Y39" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="Z39" s="130"/>
-      <c r="AA39" s="131"/>
+      <c r="Z39" s="66"/>
+      <c r="AA39" s="67"/>
     </row>
     <row r="40" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A40" s="9"/>
@@ -4186,21 +4186,21 @@
       <c r="I41" s="16"/>
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
-      <c r="M41" s="73"/>
-      <c r="N41" s="74"/>
-      <c r="O41" s="75"/>
-      <c r="P41" s="73"/>
-      <c r="Q41" s="74"/>
-      <c r="R41" s="75"/>
-      <c r="S41" s="73"/>
-      <c r="T41" s="74"/>
-      <c r="U41" s="75"/>
-      <c r="V41" s="73"/>
-      <c r="W41" s="74"/>
-      <c r="X41" s="75"/>
-      <c r="Y41" s="73"/>
-      <c r="Z41" s="74"/>
-      <c r="AA41" s="75"/>
+      <c r="M41" s="137"/>
+      <c r="N41" s="138"/>
+      <c r="O41" s="139"/>
+      <c r="P41" s="137"/>
+      <c r="Q41" s="138"/>
+      <c r="R41" s="139"/>
+      <c r="S41" s="137"/>
+      <c r="T41" s="138"/>
+      <c r="U41" s="139"/>
+      <c r="V41" s="137"/>
+      <c r="W41" s="138"/>
+      <c r="X41" s="139"/>
+      <c r="Y41" s="137"/>
+      <c r="Z41" s="138"/>
+      <c r="AA41" s="139"/>
     </row>
     <row r="42" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A42" s="9"/>
@@ -4264,28 +4264,28 @@
       <c r="M44" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="N44" s="71"/>
-      <c r="O44" s="72"/>
+      <c r="N44" s="144"/>
+      <c r="O44" s="145"/>
       <c r="P44" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="Q44" s="71"/>
-      <c r="R44" s="72"/>
+      <c r="Q44" s="144"/>
+      <c r="R44" s="145"/>
       <c r="S44" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="T44" s="71"/>
-      <c r="U44" s="72"/>
+      <c r="T44" s="144"/>
+      <c r="U44" s="145"/>
       <c r="V44" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="W44" s="71"/>
-      <c r="X44" s="72"/>
+      <c r="W44" s="144"/>
+      <c r="X44" s="145"/>
       <c r="Y44" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="Z44" s="71"/>
-      <c r="AA44" s="72"/>
+      <c r="Z44" s="144"/>
+      <c r="AA44" s="145"/>
     </row>
     <row r="45" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A45" s="1" t="s">
@@ -4332,142 +4332,6 @@
     </row>
   </sheetData>
   <mergeCells count="159">
-    <mergeCell ref="Y39:AA39"/>
-    <mergeCell ref="S37:T37"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="M39:O39"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="S39:U39"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="U37:X37"/>
-    <mergeCell ref="Y37:AA37"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="S28:T28"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:J18"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="S17:T18"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="W7:Z7"/>
-    <mergeCell ref="W8:Z8"/>
-    <mergeCell ref="W9:Z9"/>
-    <mergeCell ref="D3:M3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="X3:AA3"/>
-    <mergeCell ref="X4:AA4"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="O7:R10"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="D12:AA14"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="Y19:AA19"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="U20:X20"/>
-    <mergeCell ref="Y20:AA20"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="U17:X17"/>
-    <mergeCell ref="Y17:AA17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="Y18:AA18"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="Y23:AA23"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="U21:X21"/>
-    <mergeCell ref="Y21:AA21"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="U22:X22"/>
-    <mergeCell ref="Y22:AA22"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="Y27:AA27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="U28:X28"/>
-    <mergeCell ref="Y28:AA28"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="U25:X25"/>
-    <mergeCell ref="Y25:AA25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="U26:X26"/>
-    <mergeCell ref="Y26:AA26"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="U31:X31"/>
-    <mergeCell ref="Y31:AA31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="Y32:AA32"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="U29:X29"/>
-    <mergeCell ref="Y29:AA29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="U30:X30"/>
-    <mergeCell ref="Y30:AA30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="S31:T31"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="U35:X35"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="U36:X36"/>
-    <mergeCell ref="Y36:AA36"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="Y33:AA33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="Y34:AA34"/>
-    <mergeCell ref="S34:T34"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="S36:T36"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="Q44:R44"/>
-    <mergeCell ref="T44:U44"/>
-    <mergeCell ref="W44:X44"/>
-    <mergeCell ref="Z44:AA44"/>
-    <mergeCell ref="M41:O41"/>
-    <mergeCell ref="P41:R41"/>
-    <mergeCell ref="S41:U41"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="Y41:AA41"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="M29:N29"/>
     <mergeCell ref="M36:N36"/>
     <mergeCell ref="M37:N37"/>
     <mergeCell ref="M24:N24"/>
@@ -4491,6 +4355,142 @@
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="K28:L28"/>
     <mergeCell ref="K24:L24"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="Q44:R44"/>
+    <mergeCell ref="T44:U44"/>
+    <mergeCell ref="W44:X44"/>
+    <mergeCell ref="Z44:AA44"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="P41:R41"/>
+    <mergeCell ref="S41:U41"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="Y41:AA41"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="U35:X35"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="U36:X36"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="Y33:AA33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="Y34:AA34"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="S36:T36"/>
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="Y31:AA31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="Y32:AA32"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="Y29:AA29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="Y30:AA30"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="S31:T31"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="Y27:AA27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="Y28:AA28"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="Y25:AA25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="Y26:AA26"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="Y23:AA23"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="Y21:AA21"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="U22:X22"/>
+    <mergeCell ref="Y22:AA22"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="D12:AA14"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="U20:X20"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="U17:X17"/>
+    <mergeCell ref="Y17:AA17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="Y18:AA18"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="W8:Z8"/>
+    <mergeCell ref="W9:Z9"/>
+    <mergeCell ref="D3:M3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="X3:AA3"/>
+    <mergeCell ref="X4:AA4"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="O7:R10"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:J18"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="S17:T18"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="Y39:AA39"/>
+    <mergeCell ref="S37:T37"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="S39:U39"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="U37:X37"/>
+    <mergeCell ref="Y37:AA37"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.15748031496062992" bottom="0" header="0.27559055118110237" footer="0.31496062992125984"/>

--- a/template_form.xlsx
+++ b/template_form.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\THANAWAT\TRAININGPYTHON\ECR_System(EMAILALERT)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FFF925C-0E8B-41BA-AF91-1B025A707E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E6DEAD-336A-4D16-9612-822A14DFF0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7BEAB80B-3CB0-4569-BAF5-EBDFCCF99681}"/>
   </bookViews>
@@ -932,37 +932,190 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -977,203 +1130,50 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1577,74 +1577,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>186690</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Text Box 64">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C71812C-F02C-2B74-E3BC-AD601E561413}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1203960" y="53340"/>
-          <a:ext cx="4701540" cy="400050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="36576" bIns="27432" anchor="ctr" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1" i="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>RELATED DOCUMENT CHANGE CONTROL SHEET</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>99060</xdr:colOff>
       <xdr:row>39</xdr:row>
@@ -1953,168 +1885,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>236220</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>236220</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22474" name="Line 113">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8E30E7C-1432-D53C-B366-AEE5A235E05C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="815340" y="11445240"/>
-          <a:ext cx="518160" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd type="triangle" w="med" len="med"/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>45720</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>45720</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22475" name="Line 114">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB412ED2-C7D2-72F1-1F0C-BBC3DFD4D606}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1661160" y="11445240"/>
-          <a:ext cx="518160" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd type="triangle" w="med" len="med"/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>220980</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22476" name="Line 116">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41A99A1E-0AE5-75CA-3611-286B0E774EB9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3169920" y="11445240"/>
-          <a:ext cx="480060" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd type="triangle" w="med" len="med"/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>253365</xdr:colOff>
       <xdr:row>50</xdr:row>
@@ -2296,60 +2066,6 @@
               <a:headEnd/>
               <a:tailEnd/>
             </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22489" name="Line 114">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC7C3346-EDB6-F0EA-E395-40053EC0CC46}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2392680" y="11445240"/>
-          <a:ext cx="518160" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd type="triangle" w="med" len="med"/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
           </a:ext>
         </a:extLst>
       </xdr:spPr>
@@ -2608,58 +2324,268 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>220980</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>171112</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>205777</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22497" name="Line 116">
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B712DC74-5437-D643-FDD2-A37363316095}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0F62FE0-9B57-C757-F702-2B5AB91E4EA0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="4251960" y="11445240"/>
-          <a:ext cx="480060" cy="0"/>
+          <a:off x="998220" y="45720"/>
+          <a:ext cx="4895512" cy="426757"/>
         </a:xfrm>
-        <a:prstGeom prst="line">
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd type="triangle" w="med" len="med"/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
-    </xdr:sp>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>25960</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>219470</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94E5499A-476D-47EF-4EF3-604688506C00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="784860" y="11300460"/>
+          <a:ext cx="597460" cy="158510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>117400</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>211850</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33022110-C273-4D76-B464-07D7A6019B94}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1653540" y="11292840"/>
+          <a:ext cx="597460" cy="158510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>48820</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>219470</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C74B3AE9-54FE-4FBF-BE65-D002EB34A027}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2362200" y="11300460"/>
+          <a:ext cx="597460" cy="158510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>94540</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>227090</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACF65E8A-1BF9-4FF4-8485-5BB167D80D57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3185160" y="11308080"/>
+          <a:ext cx="597460" cy="158510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>79300</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>211850</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05FCA7AE-4487-4DC8-80D4-5DDDFB621FED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4259580" y="11292840"/>
+          <a:ext cx="597460" cy="158510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3029,64 +2955,64 @@
       <c r="A3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="98"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="111"/>
       <c r="N3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99"/>
+      <c r="P3" s="112"/>
+      <c r="Q3" s="112"/>
+      <c r="R3" s="112"/>
+      <c r="S3" s="112"/>
       <c r="U3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="X3" s="101"/>
-      <c r="Y3" s="101"/>
-      <c r="Z3" s="101"/>
-      <c r="AA3" s="101"/>
+      <c r="X3" s="114"/>
+      <c r="Y3" s="114"/>
+      <c r="Z3" s="114"/>
+      <c r="AA3" s="114"/>
     </row>
     <row r="4" spans="1:37" s="22" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="100"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
       <c r="U4" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
+      <c r="X4" s="113"/>
+      <c r="Y4" s="113"/>
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
     </row>
     <row r="5" spans="1:37" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
       <c r="M5" s="2"/>
       <c r="P5" s="2" t="s">
         <v>64</v>
@@ -3104,15 +3030,15 @@
     </row>
     <row r="6" spans="1:37" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="7" spans="1:37" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="109" t="s">
+      <c r="A7" s="122" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="102" t="s">
+      <c r="B7" s="123"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="115" t="s">
         <v>25</v>
       </c>
       <c r="H7" s="60"/>
@@ -3121,12 +3047,12 @@
       <c r="K7" s="60"/>
       <c r="L7" s="60"/>
       <c r="M7" s="61"/>
-      <c r="O7" s="85" t="s">
+      <c r="O7" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="P7" s="87"/>
-      <c r="Q7" s="87"/>
-      <c r="R7" s="88"/>
+      <c r="P7" s="97"/>
+      <c r="Q7" s="97"/>
+      <c r="R7" s="98"/>
       <c r="S7" s="54" t="s">
         <v>41</v>
       </c>
@@ -3135,32 +3061,32 @@
       <c r="V7" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="W7" s="96"/>
-      <c r="X7" s="96"/>
-      <c r="Y7" s="96"/>
-      <c r="Z7" s="96"/>
+      <c r="W7" s="109"/>
+      <c r="X7" s="109"/>
+      <c r="Y7" s="109"/>
+      <c r="Z7" s="109"/>
       <c r="AA7" s="20"/>
     </row>
     <row r="8" spans="1:37" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="111" t="s">
+      <c r="A8" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="112"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="94"/>
-      <c r="K8" s="94"/>
-      <c r="L8" s="94"/>
-      <c r="M8" s="95"/>
-      <c r="O8" s="104"/>
-      <c r="P8" s="105"/>
-      <c r="Q8" s="105"/>
-      <c r="R8" s="106"/>
+      <c r="B8" s="125"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="116"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="107"/>
+      <c r="K8" s="107"/>
+      <c r="L8" s="107"/>
+      <c r="M8" s="108"/>
+      <c r="O8" s="117"/>
+      <c r="P8" s="118"/>
+      <c r="Q8" s="118"/>
+      <c r="R8" s="119"/>
       <c r="S8" s="38" t="s">
         <v>27</v>
       </c>
@@ -3168,32 +3094,32 @@
       <c r="V8" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="W8" s="97"/>
-      <c r="X8" s="97"/>
-      <c r="Y8" s="97"/>
-      <c r="Z8" s="97"/>
+      <c r="W8" s="110"/>
+      <c r="X8" s="110"/>
+      <c r="Y8" s="110"/>
+      <c r="Z8" s="110"/>
       <c r="AA8" s="23"/>
     </row>
     <row r="9" spans="1:37" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="107" t="s">
+      <c r="A9" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="108"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="103"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="116"/>
       <c r="H9" s="52"/>
       <c r="I9" s="52"/>
       <c r="J9" s="52"/>
       <c r="K9" s="52"/>
       <c r="L9" s="52"/>
       <c r="M9" s="62"/>
-      <c r="O9" s="104"/>
-      <c r="P9" s="105"/>
-      <c r="Q9" s="105"/>
-      <c r="R9" s="106"/>
+      <c r="O9" s="117"/>
+      <c r="P9" s="118"/>
+      <c r="Q9" s="118"/>
+      <c r="R9" s="119"/>
       <c r="S9" s="38" t="s">
         <v>28</v>
       </c>
@@ -3201,10 +3127,10 @@
       <c r="V9" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="W9" s="97"/>
-      <c r="X9" s="97"/>
-      <c r="Y9" s="97"/>
-      <c r="Z9" s="97"/>
+      <c r="W9" s="110"/>
+      <c r="X9" s="110"/>
+      <c r="Y9" s="110"/>
+      <c r="Z9" s="110"/>
       <c r="AA9" s="23"/>
     </row>
     <row r="10" spans="1:37" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
@@ -3221,10 +3147,10 @@
       <c r="K10" s="36"/>
       <c r="L10" s="36"/>
       <c r="M10" s="37"/>
-      <c r="O10" s="86"/>
-      <c r="P10" s="89"/>
-      <c r="Q10" s="89"/>
-      <c r="R10" s="90"/>
+      <c r="O10" s="101"/>
+      <c r="P10" s="102"/>
+      <c r="Q10" s="102"/>
+      <c r="R10" s="103"/>
       <c r="S10" s="24"/>
       <c r="T10" s="24"/>
       <c r="U10" s="18"/>
@@ -3244,85 +3170,85 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="113"/>
-      <c r="E12" s="113"/>
-      <c r="F12" s="113"/>
-      <c r="G12" s="113"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="113"/>
-      <c r="J12" s="113"/>
-      <c r="K12" s="113"/>
-      <c r="L12" s="113"/>
-      <c r="M12" s="113"/>
-      <c r="N12" s="113"/>
-      <c r="O12" s="113"/>
-      <c r="P12" s="113"/>
-      <c r="Q12" s="113"/>
-      <c r="R12" s="113"/>
-      <c r="S12" s="113"/>
-      <c r="T12" s="113"/>
-      <c r="U12" s="113"/>
-      <c r="V12" s="113"/>
-      <c r="W12" s="113"/>
-      <c r="X12" s="113"/>
-      <c r="Y12" s="113"/>
-      <c r="Z12" s="113"/>
-      <c r="AA12" s="114"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="142"/>
+      <c r="L12" s="142"/>
+      <c r="M12" s="142"/>
+      <c r="N12" s="142"/>
+      <c r="O12" s="142"/>
+      <c r="P12" s="142"/>
+      <c r="Q12" s="142"/>
+      <c r="R12" s="142"/>
+      <c r="S12" s="142"/>
+      <c r="T12" s="142"/>
+      <c r="U12" s="142"/>
+      <c r="V12" s="142"/>
+      <c r="W12" s="142"/>
+      <c r="X12" s="142"/>
+      <c r="Y12" s="142"/>
+      <c r="Z12" s="142"/>
+      <c r="AA12" s="144"/>
     </row>
     <row r="13" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="31"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="115"/>
-      <c r="K13" s="115"/>
-      <c r="L13" s="115"/>
-      <c r="M13" s="115"/>
-      <c r="N13" s="115"/>
-      <c r="O13" s="115"/>
-      <c r="P13" s="115"/>
-      <c r="Q13" s="115"/>
-      <c r="R13" s="115"/>
-      <c r="S13" s="115"/>
-      <c r="T13" s="115"/>
-      <c r="U13" s="115"/>
-      <c r="V13" s="115"/>
-      <c r="W13" s="115"/>
-      <c r="X13" s="115"/>
-      <c r="Y13" s="115"/>
-      <c r="Z13" s="115"/>
-      <c r="AA13" s="116"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="143"/>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="143"/>
+      <c r="L13" s="143"/>
+      <c r="M13" s="143"/>
+      <c r="N13" s="143"/>
+      <c r="O13" s="143"/>
+      <c r="P13" s="143"/>
+      <c r="Q13" s="143"/>
+      <c r="R13" s="143"/>
+      <c r="S13" s="143"/>
+      <c r="T13" s="143"/>
+      <c r="U13" s="143"/>
+      <c r="V13" s="143"/>
+      <c r="W13" s="143"/>
+      <c r="X13" s="143"/>
+      <c r="Y13" s="143"/>
+      <c r="Z13" s="143"/>
+      <c r="AA13" s="145"/>
     </row>
     <row r="14" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A14" s="31"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="115"/>
-      <c r="K14" s="115"/>
-      <c r="L14" s="115"/>
-      <c r="M14" s="115"/>
-      <c r="N14" s="115"/>
-      <c r="O14" s="115"/>
-      <c r="P14" s="115"/>
-      <c r="Q14" s="115"/>
-      <c r="R14" s="115"/>
-      <c r="S14" s="115"/>
-      <c r="T14" s="115"/>
-      <c r="U14" s="115"/>
-      <c r="V14" s="115"/>
-      <c r="W14" s="115"/>
-      <c r="X14" s="115"/>
-      <c r="Y14" s="115"/>
-      <c r="Z14" s="115"/>
-      <c r="AA14" s="116"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="143"/>
+      <c r="G14" s="143"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="143"/>
+      <c r="K14" s="143"/>
+      <c r="L14" s="143"/>
+      <c r="M14" s="143"/>
+      <c r="N14" s="143"/>
+      <c r="O14" s="143"/>
+      <c r="P14" s="143"/>
+      <c r="Q14" s="143"/>
+      <c r="R14" s="143"/>
+      <c r="S14" s="143"/>
+      <c r="T14" s="143"/>
+      <c r="U14" s="143"/>
+      <c r="V14" s="143"/>
+      <c r="W14" s="143"/>
+      <c r="X14" s="143"/>
+      <c r="Y14" s="143"/>
+      <c r="Z14" s="143"/>
+      <c r="AA14" s="145"/>
     </row>
     <row r="15" spans="1:37" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A15" s="5"/>
@@ -3355,86 +3281,86 @@
     </row>
     <row r="16" spans="1:37" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="17" spans="1:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A17" s="85" t="s">
+      <c r="A17" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="85" t="s">
+      <c r="B17" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="87"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="87"/>
-      <c r="F17" s="87"/>
-      <c r="G17" s="87"/>
-      <c r="H17" s="87"/>
-      <c r="I17" s="87"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="91" t="s">
+      <c r="C17" s="97"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="97"/>
+      <c r="F17" s="97"/>
+      <c r="G17" s="97"/>
+      <c r="H17" s="97"/>
+      <c r="I17" s="97"/>
+      <c r="J17" s="98"/>
+      <c r="K17" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="L17" s="92"/>
-      <c r="M17" s="92"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="85" t="s">
+      <c r="L17" s="126"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="100"/>
+      <c r="O17" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="P17" s="87"/>
-      <c r="Q17" s="87"/>
-      <c r="R17" s="88"/>
-      <c r="S17" s="85" t="s">
+      <c r="P17" s="97"/>
+      <c r="Q17" s="97"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="T17" s="88"/>
-      <c r="U17" s="85" t="s">
+      <c r="T17" s="98"/>
+      <c r="U17" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="V17" s="87"/>
-      <c r="W17" s="87"/>
-      <c r="X17" s="87"/>
-      <c r="Y17" s="85" t="s">
+      <c r="V17" s="97"/>
+      <c r="W17" s="97"/>
+      <c r="X17" s="97"/>
+      <c r="Y17" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="Z17" s="87"/>
-      <c r="AA17" s="88"/>
+      <c r="Z17" s="97"/>
+      <c r="AA17" s="98"/>
     </row>
     <row r="18" spans="1:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A18" s="86"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="89"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="90"/>
-      <c r="K18" s="91" t="s">
+      <c r="A18" s="101"/>
+      <c r="B18" s="101"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="103"/>
+      <c r="K18" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="L18" s="93"/>
-      <c r="M18" s="91" t="s">
+      <c r="L18" s="100"/>
+      <c r="M18" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="93"/>
-      <c r="O18" s="86" t="s">
+      <c r="N18" s="100"/>
+      <c r="O18" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="P18" s="89"/>
-      <c r="Q18" s="89"/>
-      <c r="R18" s="90"/>
-      <c r="S18" s="86"/>
-      <c r="T18" s="90"/>
-      <c r="U18" s="128" t="s">
+      <c r="P18" s="102"/>
+      <c r="Q18" s="102"/>
+      <c r="R18" s="103"/>
+      <c r="S18" s="101"/>
+      <c r="T18" s="103"/>
+      <c r="U18" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="129"/>
-      <c r="W18" s="129"/>
-      <c r="X18" s="129"/>
-      <c r="Y18" s="128" t="s">
+      <c r="V18" s="105"/>
+      <c r="W18" s="105"/>
+      <c r="X18" s="105"/>
+      <c r="Y18" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="Z18" s="129"/>
-      <c r="AA18" s="130"/>
+      <c r="Z18" s="105"/>
+      <c r="AA18" s="106"/>
     </row>
     <row r="19" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A19" s="8">
@@ -3451,25 +3377,25 @@
       <c r="H19" s="40"/>
       <c r="I19" s="40"/>
       <c r="J19" s="41"/>
-      <c r="K19" s="126"/>
-      <c r="L19" s="127"/>
-      <c r="M19" s="126"/>
-      <c r="N19" s="127"/>
-      <c r="O19" s="117"/>
-      <c r="P19" s="118"/>
-      <c r="Q19" s="118"/>
-      <c r="R19" s="119"/>
-      <c r="S19" s="117" t="s">
+      <c r="K19" s="94"/>
+      <c r="L19" s="95"/>
+      <c r="M19" s="94"/>
+      <c r="N19" s="95"/>
+      <c r="O19" s="88"/>
+      <c r="P19" s="89"/>
+      <c r="Q19" s="89"/>
+      <c r="R19" s="90"/>
+      <c r="S19" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="T19" s="119"/>
-      <c r="U19" s="120"/>
-      <c r="V19" s="121"/>
-      <c r="W19" s="121"/>
-      <c r="X19" s="122"/>
-      <c r="Y19" s="120"/>
-      <c r="Z19" s="121"/>
-      <c r="AA19" s="122"/>
+      <c r="T19" s="90"/>
+      <c r="U19" s="91"/>
+      <c r="V19" s="92"/>
+      <c r="W19" s="92"/>
+      <c r="X19" s="93"/>
+      <c r="Y19" s="91"/>
+      <c r="Z19" s="92"/>
+      <c r="AA19" s="93"/>
     </row>
     <row r="20" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="11">
@@ -3486,25 +3412,25 @@
       <c r="H20" s="43"/>
       <c r="I20" s="43"/>
       <c r="J20" s="44"/>
-      <c r="K20" s="83"/>
-      <c r="L20" s="84"/>
-      <c r="M20" s="83"/>
-      <c r="N20" s="84"/>
-      <c r="O20" s="80"/>
-      <c r="P20" s="81"/>
-      <c r="Q20" s="81"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="80" t="s">
+      <c r="K20" s="65"/>
+      <c r="L20" s="66"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="76"/>
+      <c r="P20" s="77"/>
+      <c r="Q20" s="77"/>
+      <c r="R20" s="78"/>
+      <c r="S20" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="T20" s="82"/>
-      <c r="U20" s="123"/>
-      <c r="V20" s="124"/>
-      <c r="W20" s="124"/>
-      <c r="X20" s="125"/>
-      <c r="Y20" s="123"/>
-      <c r="Z20" s="124"/>
-      <c r="AA20" s="125"/>
+      <c r="T20" s="78"/>
+      <c r="U20" s="79"/>
+      <c r="V20" s="80"/>
+      <c r="W20" s="80"/>
+      <c r="X20" s="81"/>
+      <c r="Y20" s="79"/>
+      <c r="Z20" s="80"/>
+      <c r="AA20" s="81"/>
     </row>
     <row r="21" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A21" s="11">
@@ -3521,25 +3447,25 @@
       <c r="H21" s="43"/>
       <c r="I21" s="43"/>
       <c r="J21" s="44"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="84"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="84"/>
-      <c r="O21" s="80"/>
-      <c r="P21" s="81"/>
-      <c r="Q21" s="81"/>
-      <c r="R21" s="82"/>
-      <c r="S21" s="80" t="s">
+      <c r="K21" s="65"/>
+      <c r="L21" s="66"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="66"/>
+      <c r="O21" s="76"/>
+      <c r="P21" s="77"/>
+      <c r="Q21" s="77"/>
+      <c r="R21" s="78"/>
+      <c r="S21" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="T21" s="82"/>
-      <c r="U21" s="123"/>
-      <c r="V21" s="124"/>
-      <c r="W21" s="124"/>
-      <c r="X21" s="125"/>
-      <c r="Y21" s="123"/>
-      <c r="Z21" s="124"/>
-      <c r="AA21" s="125"/>
+      <c r="T21" s="78"/>
+      <c r="U21" s="79"/>
+      <c r="V21" s="80"/>
+      <c r="W21" s="80"/>
+      <c r="X21" s="81"/>
+      <c r="Y21" s="79"/>
+      <c r="Z21" s="80"/>
+      <c r="AA21" s="81"/>
     </row>
     <row r="22" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="11">
@@ -3556,25 +3482,25 @@
       <c r="H22" s="43"/>
       <c r="I22" s="43"/>
       <c r="J22" s="44"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="80"/>
-      <c r="P22" s="81"/>
-      <c r="Q22" s="81"/>
-      <c r="R22" s="82"/>
-      <c r="S22" s="80" t="s">
+      <c r="K22" s="65"/>
+      <c r="L22" s="66"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="76"/>
+      <c r="P22" s="77"/>
+      <c r="Q22" s="77"/>
+      <c r="R22" s="78"/>
+      <c r="S22" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="T22" s="82"/>
-      <c r="U22" s="123"/>
-      <c r="V22" s="124"/>
-      <c r="W22" s="124"/>
-      <c r="X22" s="125"/>
-      <c r="Y22" s="123"/>
-      <c r="Z22" s="124"/>
-      <c r="AA22" s="125"/>
+      <c r="T22" s="78"/>
+      <c r="U22" s="79"/>
+      <c r="V22" s="80"/>
+      <c r="W22" s="80"/>
+      <c r="X22" s="81"/>
+      <c r="Y22" s="79"/>
+      <c r="Z22" s="80"/>
+      <c r="AA22" s="81"/>
     </row>
     <row r="23" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A23" s="11">
@@ -3591,34 +3517,34 @@
       <c r="H23" s="43"/>
       <c r="I23" s="43"/>
       <c r="J23" s="44"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="83"/>
-      <c r="N23" s="84"/>
-      <c r="O23" s="80"/>
-      <c r="P23" s="81"/>
-      <c r="Q23" s="81"/>
-      <c r="R23" s="82"/>
-      <c r="S23" s="80" t="s">
+      <c r="K23" s="65"/>
+      <c r="L23" s="66"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="76"/>
+      <c r="P23" s="77"/>
+      <c r="Q23" s="77"/>
+      <c r="R23" s="78"/>
+      <c r="S23" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="T23" s="82"/>
-      <c r="U23" s="123"/>
-      <c r="V23" s="124"/>
-      <c r="W23" s="124"/>
-      <c r="X23" s="125"/>
-      <c r="Y23" s="123"/>
-      <c r="Z23" s="124"/>
-      <c r="AA23" s="125"/>
+      <c r="T23" s="78"/>
+      <c r="U23" s="79"/>
+      <c r="V23" s="80"/>
+      <c r="W23" s="80"/>
+      <c r="X23" s="81"/>
+      <c r="Y23" s="79"/>
+      <c r="Z23" s="80"/>
+      <c r="AA23" s="81"/>
     </row>
     <row r="24" spans="1:27" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="63">
         <v>6</v>
       </c>
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="127" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="77"/>
+      <c r="C24" s="128"/>
       <c r="D24" s="45"/>
       <c r="E24" s="45"/>
       <c r="F24" s="45"/>
@@ -3626,25 +3552,25 @@
       <c r="H24" s="45"/>
       <c r="I24" s="45"/>
       <c r="J24" s="46"/>
-      <c r="K24" s="142"/>
-      <c r="L24" s="143"/>
-      <c r="M24" s="142"/>
-      <c r="N24" s="143"/>
-      <c r="O24" s="131"/>
-      <c r="P24" s="132"/>
-      <c r="Q24" s="132"/>
-      <c r="R24" s="133"/>
-      <c r="S24" s="78" t="s">
+      <c r="K24" s="69"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="82"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="84"/>
+      <c r="S24" s="129" t="s">
         <v>72</v>
       </c>
-      <c r="T24" s="79"/>
-      <c r="U24" s="134"/>
-      <c r="V24" s="135"/>
-      <c r="W24" s="135"/>
-      <c r="X24" s="136"/>
-      <c r="Y24" s="134"/>
-      <c r="Z24" s="135"/>
-      <c r="AA24" s="136"/>
+      <c r="T24" s="130"/>
+      <c r="U24" s="85"/>
+      <c r="V24" s="86"/>
+      <c r="W24" s="86"/>
+      <c r="X24" s="87"/>
+      <c r="Y24" s="85"/>
+      <c r="Z24" s="86"/>
+      <c r="AA24" s="87"/>
     </row>
     <row r="25" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="11">
@@ -3661,25 +3587,25 @@
       <c r="H25" s="43"/>
       <c r="I25" s="43"/>
       <c r="J25" s="44"/>
-      <c r="K25" s="83"/>
-      <c r="L25" s="84"/>
-      <c r="M25" s="83"/>
-      <c r="N25" s="84"/>
-      <c r="O25" s="80"/>
-      <c r="P25" s="81"/>
-      <c r="Q25" s="81"/>
-      <c r="R25" s="82"/>
-      <c r="S25" s="80" t="s">
+      <c r="K25" s="65"/>
+      <c r="L25" s="66"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="66"/>
+      <c r="O25" s="76"/>
+      <c r="P25" s="77"/>
+      <c r="Q25" s="77"/>
+      <c r="R25" s="78"/>
+      <c r="S25" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="T25" s="82"/>
-      <c r="U25" s="123"/>
-      <c r="V25" s="124"/>
-      <c r="W25" s="124"/>
-      <c r="X25" s="125"/>
-      <c r="Y25" s="123"/>
-      <c r="Z25" s="124"/>
-      <c r="AA25" s="125"/>
+      <c r="T25" s="78"/>
+      <c r="U25" s="79"/>
+      <c r="V25" s="80"/>
+      <c r="W25" s="80"/>
+      <c r="X25" s="81"/>
+      <c r="Y25" s="79"/>
+      <c r="Z25" s="80"/>
+      <c r="AA25" s="81"/>
     </row>
     <row r="26" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A26" s="11">
@@ -3696,25 +3622,25 @@
       <c r="H26" s="43"/>
       <c r="I26" s="43"/>
       <c r="J26" s="44"/>
-      <c r="K26" s="83"/>
-      <c r="L26" s="84"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="84"/>
-      <c r="O26" s="80"/>
-      <c r="P26" s="81"/>
-      <c r="Q26" s="81"/>
-      <c r="R26" s="82"/>
-      <c r="S26" s="80" t="s">
+      <c r="K26" s="65"/>
+      <c r="L26" s="66"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="66"/>
+      <c r="O26" s="76"/>
+      <c r="P26" s="77"/>
+      <c r="Q26" s="77"/>
+      <c r="R26" s="78"/>
+      <c r="S26" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="T26" s="82"/>
-      <c r="U26" s="123"/>
-      <c r="V26" s="124"/>
-      <c r="W26" s="124"/>
-      <c r="X26" s="125"/>
-      <c r="Y26" s="123"/>
-      <c r="Z26" s="124"/>
-      <c r="AA26" s="125"/>
+      <c r="T26" s="78"/>
+      <c r="U26" s="79"/>
+      <c r="V26" s="80"/>
+      <c r="W26" s="80"/>
+      <c r="X26" s="81"/>
+      <c r="Y26" s="79"/>
+      <c r="Z26" s="80"/>
+      <c r="AA26" s="81"/>
     </row>
     <row r="27" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A27" s="11">
@@ -3731,25 +3657,25 @@
       <c r="H27" s="43"/>
       <c r="I27" s="43"/>
       <c r="J27" s="44"/>
-      <c r="K27" s="83"/>
-      <c r="L27" s="84"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="84"/>
-      <c r="O27" s="80"/>
-      <c r="P27" s="81"/>
-      <c r="Q27" s="81"/>
-      <c r="R27" s="82"/>
-      <c r="S27" s="80" t="s">
+      <c r="K27" s="65"/>
+      <c r="L27" s="66"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="66"/>
+      <c r="O27" s="76"/>
+      <c r="P27" s="77"/>
+      <c r="Q27" s="77"/>
+      <c r="R27" s="78"/>
+      <c r="S27" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="T27" s="82"/>
-      <c r="U27" s="123"/>
-      <c r="V27" s="124"/>
-      <c r="W27" s="124"/>
-      <c r="X27" s="125"/>
-      <c r="Y27" s="123"/>
-      <c r="Z27" s="124"/>
-      <c r="AA27" s="125"/>
+      <c r="T27" s="78"/>
+      <c r="U27" s="79"/>
+      <c r="V27" s="80"/>
+      <c r="W27" s="80"/>
+      <c r="X27" s="81"/>
+      <c r="Y27" s="79"/>
+      <c r="Z27" s="80"/>
+      <c r="AA27" s="81"/>
     </row>
     <row r="28" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A28" s="11">
@@ -3766,25 +3692,25 @@
       <c r="H28" s="43"/>
       <c r="I28" s="43"/>
       <c r="J28" s="44"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="84"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="84"/>
-      <c r="O28" s="80"/>
-      <c r="P28" s="81"/>
-      <c r="Q28" s="81"/>
-      <c r="R28" s="82"/>
-      <c r="S28" s="80" t="s">
+      <c r="K28" s="65"/>
+      <c r="L28" s="66"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="76"/>
+      <c r="P28" s="77"/>
+      <c r="Q28" s="77"/>
+      <c r="R28" s="78"/>
+      <c r="S28" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="T28" s="82"/>
-      <c r="U28" s="123"/>
-      <c r="V28" s="124"/>
-      <c r="W28" s="124"/>
-      <c r="X28" s="125"/>
-      <c r="Y28" s="123"/>
-      <c r="Z28" s="124"/>
-      <c r="AA28" s="125"/>
+      <c r="T28" s="78"/>
+      <c r="U28" s="79"/>
+      <c r="V28" s="80"/>
+      <c r="W28" s="80"/>
+      <c r="X28" s="81"/>
+      <c r="Y28" s="79"/>
+      <c r="Z28" s="80"/>
+      <c r="AA28" s="81"/>
     </row>
     <row r="29" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A29" s="11">
@@ -3801,25 +3727,25 @@
       <c r="H29" s="43"/>
       <c r="I29" s="43"/>
       <c r="J29" s="44"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="84"/>
-      <c r="M29" s="83"/>
-      <c r="N29" s="84"/>
-      <c r="O29" s="80"/>
-      <c r="P29" s="81"/>
-      <c r="Q29" s="81"/>
-      <c r="R29" s="82"/>
-      <c r="S29" s="80" t="s">
+      <c r="K29" s="65"/>
+      <c r="L29" s="66"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="66"/>
+      <c r="O29" s="76"/>
+      <c r="P29" s="77"/>
+      <c r="Q29" s="77"/>
+      <c r="R29" s="78"/>
+      <c r="S29" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="T29" s="82"/>
-      <c r="U29" s="123"/>
-      <c r="V29" s="124"/>
-      <c r="W29" s="124"/>
-      <c r="X29" s="125"/>
-      <c r="Y29" s="123"/>
-      <c r="Z29" s="124"/>
-      <c r="AA29" s="125"/>
+      <c r="T29" s="78"/>
+      <c r="U29" s="79"/>
+      <c r="V29" s="80"/>
+      <c r="W29" s="80"/>
+      <c r="X29" s="81"/>
+      <c r="Y29" s="79"/>
+      <c r="Z29" s="80"/>
+      <c r="AA29" s="81"/>
     </row>
     <row r="30" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A30" s="11">
@@ -3836,25 +3762,25 @@
       <c r="H30" s="43"/>
       <c r="I30" s="43"/>
       <c r="J30" s="44"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="84"/>
-      <c r="M30" s="83"/>
-      <c r="N30" s="84"/>
-      <c r="O30" s="80"/>
-      <c r="P30" s="81"/>
-      <c r="Q30" s="81"/>
-      <c r="R30" s="82"/>
-      <c r="S30" s="80" t="s">
+      <c r="K30" s="65"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="66"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="77"/>
+      <c r="Q30" s="77"/>
+      <c r="R30" s="78"/>
+      <c r="S30" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="T30" s="82"/>
-      <c r="U30" s="123"/>
-      <c r="V30" s="124"/>
-      <c r="W30" s="124"/>
-      <c r="X30" s="125"/>
-      <c r="Y30" s="123"/>
-      <c r="Z30" s="124"/>
-      <c r="AA30" s="125"/>
+      <c r="T30" s="78"/>
+      <c r="U30" s="79"/>
+      <c r="V30" s="80"/>
+      <c r="W30" s="80"/>
+      <c r="X30" s="81"/>
+      <c r="Y30" s="79"/>
+      <c r="Z30" s="80"/>
+      <c r="AA30" s="81"/>
     </row>
     <row r="31" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A31" s="11">
@@ -3871,25 +3797,25 @@
       <c r="H31" s="43"/>
       <c r="I31" s="43"/>
       <c r="J31" s="44"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="84"/>
-      <c r="M31" s="83"/>
-      <c r="N31" s="84"/>
-      <c r="O31" s="80"/>
-      <c r="P31" s="81"/>
-      <c r="Q31" s="81"/>
-      <c r="R31" s="82"/>
-      <c r="S31" s="80" t="s">
+      <c r="K31" s="65"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="77"/>
+      <c r="Q31" s="77"/>
+      <c r="R31" s="78"/>
+      <c r="S31" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="T31" s="82"/>
-      <c r="U31" s="123"/>
-      <c r="V31" s="124"/>
-      <c r="W31" s="124"/>
-      <c r="X31" s="125"/>
-      <c r="Y31" s="123"/>
-      <c r="Z31" s="124"/>
-      <c r="AA31" s="125"/>
+      <c r="T31" s="78"/>
+      <c r="U31" s="79"/>
+      <c r="V31" s="80"/>
+      <c r="W31" s="80"/>
+      <c r="X31" s="81"/>
+      <c r="Y31" s="79"/>
+      <c r="Z31" s="80"/>
+      <c r="AA31" s="81"/>
     </row>
     <row r="32" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A32" s="11">
@@ -3906,25 +3832,25 @@
       <c r="H32" s="43"/>
       <c r="I32" s="43"/>
       <c r="J32" s="44"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="84"/>
-      <c r="M32" s="83"/>
-      <c r="N32" s="84"/>
-      <c r="O32" s="80"/>
-      <c r="P32" s="81"/>
-      <c r="Q32" s="81"/>
-      <c r="R32" s="82"/>
-      <c r="S32" s="80" t="s">
+      <c r="K32" s="65"/>
+      <c r="L32" s="66"/>
+      <c r="M32" s="65"/>
+      <c r="N32" s="66"/>
+      <c r="O32" s="76"/>
+      <c r="P32" s="77"/>
+      <c r="Q32" s="77"/>
+      <c r="R32" s="78"/>
+      <c r="S32" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="T32" s="82"/>
-      <c r="U32" s="123"/>
-      <c r="V32" s="124"/>
-      <c r="W32" s="124"/>
-      <c r="X32" s="125"/>
-      <c r="Y32" s="123"/>
-      <c r="Z32" s="124"/>
-      <c r="AA32" s="125"/>
+      <c r="T32" s="78"/>
+      <c r="U32" s="79"/>
+      <c r="V32" s="80"/>
+      <c r="W32" s="80"/>
+      <c r="X32" s="81"/>
+      <c r="Y32" s="79"/>
+      <c r="Z32" s="80"/>
+      <c r="AA32" s="81"/>
     </row>
     <row r="33" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A33" s="11">
@@ -3941,25 +3867,25 @@
       <c r="H33" s="43"/>
       <c r="I33" s="43"/>
       <c r="J33" s="44"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="84"/>
-      <c r="M33" s="83"/>
-      <c r="N33" s="84"/>
-      <c r="O33" s="80"/>
-      <c r="P33" s="81"/>
-      <c r="Q33" s="81"/>
-      <c r="R33" s="82"/>
-      <c r="S33" s="80" t="s">
+      <c r="K33" s="65"/>
+      <c r="L33" s="66"/>
+      <c r="M33" s="65"/>
+      <c r="N33" s="66"/>
+      <c r="O33" s="76"/>
+      <c r="P33" s="77"/>
+      <c r="Q33" s="77"/>
+      <c r="R33" s="78"/>
+      <c r="S33" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="T33" s="82"/>
-      <c r="U33" s="123"/>
-      <c r="V33" s="124"/>
-      <c r="W33" s="124"/>
-      <c r="X33" s="125"/>
-      <c r="Y33" s="123"/>
-      <c r="Z33" s="124"/>
-      <c r="AA33" s="125"/>
+      <c r="T33" s="78"/>
+      <c r="U33" s="79"/>
+      <c r="V33" s="80"/>
+      <c r="W33" s="80"/>
+      <c r="X33" s="81"/>
+      <c r="Y33" s="79"/>
+      <c r="Z33" s="80"/>
+      <c r="AA33" s="81"/>
     </row>
     <row r="34" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A34" s="11">
@@ -3976,25 +3902,25 @@
       <c r="H34" s="43"/>
       <c r="I34" s="43"/>
       <c r="J34" s="44"/>
-      <c r="K34" s="83"/>
-      <c r="L34" s="84"/>
-      <c r="M34" s="83"/>
-      <c r="N34" s="84"/>
-      <c r="O34" s="80"/>
-      <c r="P34" s="81"/>
-      <c r="Q34" s="81"/>
-      <c r="R34" s="82"/>
-      <c r="S34" s="80" t="s">
+      <c r="K34" s="65"/>
+      <c r="L34" s="66"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="66"/>
+      <c r="O34" s="76"/>
+      <c r="P34" s="77"/>
+      <c r="Q34" s="77"/>
+      <c r="R34" s="78"/>
+      <c r="S34" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="T34" s="82"/>
-      <c r="U34" s="123"/>
-      <c r="V34" s="124"/>
-      <c r="W34" s="124"/>
-      <c r="X34" s="125"/>
-      <c r="Y34" s="123"/>
-      <c r="Z34" s="124"/>
-      <c r="AA34" s="125"/>
+      <c r="T34" s="78"/>
+      <c r="U34" s="79"/>
+      <c r="V34" s="80"/>
+      <c r="W34" s="80"/>
+      <c r="X34" s="81"/>
+      <c r="Y34" s="79"/>
+      <c r="Z34" s="80"/>
+      <c r="AA34" s="81"/>
     </row>
     <row r="35" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A35" s="11">
@@ -4011,25 +3937,25 @@
       <c r="H35" s="43"/>
       <c r="I35" s="43"/>
       <c r="J35" s="44"/>
-      <c r="K35" s="83"/>
-      <c r="L35" s="84"/>
-      <c r="M35" s="83"/>
-      <c r="N35" s="84"/>
-      <c r="O35" s="80"/>
-      <c r="P35" s="81"/>
-      <c r="Q35" s="81"/>
-      <c r="R35" s="82"/>
-      <c r="S35" s="80" t="s">
+      <c r="K35" s="65"/>
+      <c r="L35" s="66"/>
+      <c r="M35" s="65"/>
+      <c r="N35" s="66"/>
+      <c r="O35" s="76"/>
+      <c r="P35" s="77"/>
+      <c r="Q35" s="77"/>
+      <c r="R35" s="78"/>
+      <c r="S35" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="T35" s="82"/>
-      <c r="U35" s="123"/>
-      <c r="V35" s="124"/>
-      <c r="W35" s="124"/>
-      <c r="X35" s="125"/>
-      <c r="Y35" s="123"/>
-      <c r="Z35" s="124"/>
-      <c r="AA35" s="125"/>
+      <c r="T35" s="78"/>
+      <c r="U35" s="79"/>
+      <c r="V35" s="80"/>
+      <c r="W35" s="80"/>
+      <c r="X35" s="81"/>
+      <c r="Y35" s="79"/>
+      <c r="Z35" s="80"/>
+      <c r="AA35" s="81"/>
     </row>
     <row r="36" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A36" s="11">
@@ -4046,25 +3972,25 @@
       <c r="H36" s="43"/>
       <c r="I36" s="43"/>
       <c r="J36" s="44"/>
-      <c r="K36" s="83"/>
-      <c r="L36" s="84"/>
-      <c r="M36" s="83"/>
-      <c r="N36" s="84"/>
-      <c r="O36" s="80"/>
-      <c r="P36" s="81"/>
-      <c r="Q36" s="81"/>
-      <c r="R36" s="82"/>
-      <c r="S36" s="80" t="s">
+      <c r="K36" s="65"/>
+      <c r="L36" s="66"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="66"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="77"/>
+      <c r="Q36" s="77"/>
+      <c r="R36" s="78"/>
+      <c r="S36" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="T36" s="82"/>
-      <c r="U36" s="123"/>
-      <c r="V36" s="124"/>
-      <c r="W36" s="124"/>
-      <c r="X36" s="125"/>
-      <c r="Y36" s="123"/>
-      <c r="Z36" s="124"/>
-      <c r="AA36" s="125"/>
+      <c r="T36" s="78"/>
+      <c r="U36" s="79"/>
+      <c r="V36" s="80"/>
+      <c r="W36" s="80"/>
+      <c r="X36" s="81"/>
+      <c r="Y36" s="79"/>
+      <c r="Z36" s="80"/>
+      <c r="AA36" s="81"/>
     </row>
     <row r="37" spans="1:27" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A37" s="29">
@@ -4081,35 +4007,35 @@
       <c r="H37" s="48"/>
       <c r="I37" s="48"/>
       <c r="J37" s="49"/>
-      <c r="K37" s="140"/>
-      <c r="L37" s="141"/>
-      <c r="M37" s="140"/>
-      <c r="N37" s="141"/>
-      <c r="O37" s="68"/>
-      <c r="P37" s="72"/>
-      <c r="Q37" s="72"/>
-      <c r="R37" s="69"/>
-      <c r="S37" s="68" t="s">
+      <c r="K37" s="67"/>
+      <c r="L37" s="68"/>
+      <c r="M37" s="67"/>
+      <c r="N37" s="68"/>
+      <c r="O37" s="134"/>
+      <c r="P37" s="138"/>
+      <c r="Q37" s="138"/>
+      <c r="R37" s="135"/>
+      <c r="S37" s="134" t="s">
         <v>34</v>
       </c>
-      <c r="T37" s="69"/>
-      <c r="U37" s="73"/>
-      <c r="V37" s="74"/>
-      <c r="W37" s="74"/>
-      <c r="X37" s="75"/>
-      <c r="Y37" s="73"/>
-      <c r="Z37" s="74"/>
-      <c r="AA37" s="75"/>
+      <c r="T37" s="135"/>
+      <c r="U37" s="139"/>
+      <c r="V37" s="140"/>
+      <c r="W37" s="140"/>
+      <c r="X37" s="141"/>
+      <c r="Y37" s="139"/>
+      <c r="Z37" s="140"/>
+      <c r="AA37" s="141"/>
     </row>
     <row r="38" spans="1:27" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="39" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="70" t="s">
+      <c r="A39" s="136" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
+      <c r="B39" s="137"/>
+      <c r="C39" s="137"/>
+      <c r="D39" s="137"/>
+      <c r="E39" s="137"/>
       <c r="F39" s="56"/>
       <c r="G39" s="57" t="s">
         <v>23</v>
@@ -4119,31 +4045,31 @@
       <c r="J39" s="54"/>
       <c r="K39" s="56"/>
       <c r="L39" s="55"/>
-      <c r="M39" s="65" t="s">
+      <c r="M39" s="131" t="s">
         <v>38</v>
       </c>
-      <c r="N39" s="66"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="65" t="s">
+      <c r="N39" s="132"/>
+      <c r="O39" s="133"/>
+      <c r="P39" s="131" t="s">
         <v>58</v>
       </c>
-      <c r="Q39" s="66"/>
-      <c r="R39" s="67"/>
-      <c r="S39" s="65" t="s">
+      <c r="Q39" s="132"/>
+      <c r="R39" s="133"/>
+      <c r="S39" s="131" t="s">
         <v>63</v>
       </c>
-      <c r="T39" s="66"/>
-      <c r="U39" s="67"/>
-      <c r="V39" s="66" t="s">
+      <c r="T39" s="132"/>
+      <c r="U39" s="133"/>
+      <c r="V39" s="132" t="s">
         <v>69</v>
       </c>
-      <c r="W39" s="66"/>
-      <c r="X39" s="67"/>
-      <c r="Y39" s="65" t="s">
+      <c r="W39" s="132"/>
+      <c r="X39" s="133"/>
+      <c r="Y39" s="131" t="s">
         <v>39</v>
       </c>
-      <c r="Z39" s="66"/>
-      <c r="AA39" s="67"/>
+      <c r="Z39" s="132"/>
+      <c r="AA39" s="133"/>
     </row>
     <row r="40" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A40" s="9"/>
@@ -4186,21 +4112,21 @@
       <c r="I41" s="16"/>
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
-      <c r="M41" s="137"/>
-      <c r="N41" s="138"/>
-      <c r="O41" s="139"/>
-      <c r="P41" s="137"/>
-      <c r="Q41" s="138"/>
-      <c r="R41" s="139"/>
-      <c r="S41" s="137"/>
-      <c r="T41" s="138"/>
-      <c r="U41" s="139"/>
-      <c r="V41" s="137"/>
-      <c r="W41" s="138"/>
-      <c r="X41" s="139"/>
-      <c r="Y41" s="137"/>
-      <c r="Z41" s="138"/>
-      <c r="AA41" s="139"/>
+      <c r="M41" s="73"/>
+      <c r="N41" s="74"/>
+      <c r="O41" s="75"/>
+      <c r="P41" s="73"/>
+      <c r="Q41" s="74"/>
+      <c r="R41" s="75"/>
+      <c r="S41" s="73"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="73"/>
+      <c r="W41" s="74"/>
+      <c r="X41" s="75"/>
+      <c r="Y41" s="73"/>
+      <c r="Z41" s="74"/>
+      <c r="AA41" s="75"/>
     </row>
     <row r="42" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A42" s="9"/>
@@ -4264,28 +4190,28 @@
       <c r="M44" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="N44" s="144"/>
-      <c r="O44" s="145"/>
+      <c r="N44" s="71"/>
+      <c r="O44" s="72"/>
       <c r="P44" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="Q44" s="144"/>
-      <c r="R44" s="145"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
       <c r="S44" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="T44" s="144"/>
-      <c r="U44" s="145"/>
+      <c r="T44" s="71"/>
+      <c r="U44" s="72"/>
       <c r="V44" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="W44" s="144"/>
-      <c r="X44" s="145"/>
+      <c r="W44" s="71"/>
+      <c r="X44" s="72"/>
       <c r="Y44" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="Z44" s="144"/>
-      <c r="AA44" s="145"/>
+      <c r="Z44" s="71"/>
+      <c r="AA44" s="72"/>
     </row>
     <row r="45" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A45" s="1" t="s">
@@ -4331,7 +4257,144 @@
       <c r="AA49" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="159">
+  <mergeCells count="160">
+    <mergeCell ref="Y39:AA39"/>
+    <mergeCell ref="S37:T37"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="S39:U39"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="U37:X37"/>
+    <mergeCell ref="Y37:AA37"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:J18"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="S17:T18"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="W8:Z8"/>
+    <mergeCell ref="W9:Z9"/>
+    <mergeCell ref="D3:M3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="X3:AA3"/>
+    <mergeCell ref="X4:AA4"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="O7:R10"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="U20:X20"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="U17:X17"/>
+    <mergeCell ref="Y17:AA17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="Y18:AA18"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="D12:Q14"/>
+    <mergeCell ref="R12:AA14"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="Y23:AA23"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="Y21:AA21"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="U22:X22"/>
+    <mergeCell ref="Y22:AA22"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="Y27:AA27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="Y28:AA28"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="Y25:AA25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="Y26:AA26"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="Y31:AA31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="Y32:AA32"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="Y29:AA29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="Y30:AA30"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="S31:T31"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="U35:X35"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="U36:X36"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="Y33:AA33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="Y34:AA34"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="S36:T36"/>
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="Q44:R44"/>
+    <mergeCell ref="T44:U44"/>
+    <mergeCell ref="W44:X44"/>
+    <mergeCell ref="Z44:AA44"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="P41:R41"/>
+    <mergeCell ref="S41:U41"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="Y41:AA41"/>
     <mergeCell ref="M36:N36"/>
     <mergeCell ref="M37:N37"/>
     <mergeCell ref="M24:N24"/>
@@ -4355,142 +4418,6 @@
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="K28:L28"/>
     <mergeCell ref="K24:L24"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="Q44:R44"/>
-    <mergeCell ref="T44:U44"/>
-    <mergeCell ref="W44:X44"/>
-    <mergeCell ref="Z44:AA44"/>
-    <mergeCell ref="M41:O41"/>
-    <mergeCell ref="P41:R41"/>
-    <mergeCell ref="S41:U41"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="Y41:AA41"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="U35:X35"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="U36:X36"/>
-    <mergeCell ref="Y36:AA36"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="Y33:AA33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="Y34:AA34"/>
-    <mergeCell ref="S34:T34"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="S36:T36"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="U31:X31"/>
-    <mergeCell ref="Y31:AA31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="Y32:AA32"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="U29:X29"/>
-    <mergeCell ref="Y29:AA29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="U30:X30"/>
-    <mergeCell ref="Y30:AA30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="S31:T31"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="Y27:AA27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="U28:X28"/>
-    <mergeCell ref="Y28:AA28"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="U25:X25"/>
-    <mergeCell ref="Y25:AA25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="U26:X26"/>
-    <mergeCell ref="Y26:AA26"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="Y23:AA23"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="U21:X21"/>
-    <mergeCell ref="Y21:AA21"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="U22:X22"/>
-    <mergeCell ref="Y22:AA22"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="D12:AA14"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="Y19:AA19"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="U20:X20"/>
-    <mergeCell ref="Y20:AA20"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="U17:X17"/>
-    <mergeCell ref="Y17:AA17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="Y18:AA18"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="W7:Z7"/>
-    <mergeCell ref="W8:Z8"/>
-    <mergeCell ref="W9:Z9"/>
-    <mergeCell ref="D3:M3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="X3:AA3"/>
-    <mergeCell ref="X4:AA4"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="O7:R10"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:J18"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="S17:T18"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="S28:T28"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="Y39:AA39"/>
-    <mergeCell ref="S37:T37"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="M39:O39"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="S39:U39"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="U37:X37"/>
-    <mergeCell ref="Y37:AA37"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.15748031496062992" bottom="0" header="0.27559055118110237" footer="0.31496062992125984"/>

--- a/template_form.xlsx
+++ b/template_form.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\THANAWAT\TRAININGPYTHON\ECR_System(EMAILALERT)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E6DEAD-336A-4D16-9612-822A14DFF0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40586EB-7F5B-41FC-80A7-667CC48B7CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7BEAB80B-3CB0-4569-BAF5-EBDFCCF99681}"/>
   </bookViews>
@@ -2327,15 +2327,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>160020</xdr:colOff>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>171112</xdr:colOff>
+      <xdr:colOff>201592</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>205777</xdr:rowOff>
+      <xdr:rowOff>243877</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2358,7 +2358,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="998220" y="45720"/>
+          <a:off x="1028700" y="83820"/>
           <a:ext cx="4895512" cy="426757"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
